--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J121-RolePriseCharge-ENREG.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J121-RolePriseCharge-ENREG.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="139">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250425120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,12 +141,6 @@
     <t>Préparateur en pharmacie (officine)</t>
   </si>
   <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>Auxiliaire de vie sociale</t>
-  </si>
-  <si>
     <t>319</t>
   </si>
   <si>
@@ -169,12 +163,6 @@
   </si>
   <si>
     <t>Assistant familial</t>
-  </si>
-  <si>
-    <t>323</t>
-  </si>
-  <si>
-    <t>Aide médico-psychologique (AMP)</t>
   </si>
   <si>
     <t>324</t>
@@ -703,7 +691,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1155,31 +1143,15 @@
         <v>136</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>142</v>
       </c>
     </row>
   </sheetData>
